--- a/output/tables/structure/finished_tables/Wood_plains_assignment.xlsx
+++ b/output/tables/structure/finished_tables/Wood_plains_assignment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\R_WD\revised_bison_popgen\output\tables\structure\finished_tables\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\D_RWD\revised_bison_popgen\output\tables\STRUCTURE\finished_tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA95DA8-A32D-42A0-9F58-C15B357D8265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55F6CB5-00D9-4AB3-8921-61D3CABA5661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-118" yWindow="-118" windowWidth="20343" windowHeight="12934" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -404,7 +404,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -412,24 +430,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -712,12 +712,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="10.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="8.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.28515625" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="8.85546875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
@@ -733,7 +733,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -747,19 +747,19 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="10"/>
-      <c r="B3" s="13" t="s">
+      <c r="A3" s="16"/>
+      <c r="B3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="11" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
+      <c r="A4" s="16"/>
       <c r="B4" s="7" t="s">
         <v>5</v>
       </c>
@@ -771,19 +771,19 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="10"/>
-      <c r="B5" s="13" t="s">
+      <c r="A5" s="16"/>
+      <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
+      <c r="A6" s="16"/>
       <c r="B6" s="7" t="s">
         <v>7</v>
       </c>
@@ -795,19 +795,19 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
-      <c r="B7" s="13" t="s">
+      <c r="A7" s="16"/>
+      <c r="B7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="11" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
+      <c r="A8" s="16"/>
       <c r="B8" s="7" t="s">
         <v>9</v>
       </c>
@@ -819,19 +819,19 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="13" t="s">
+      <c r="A9" s="16"/>
+      <c r="B9" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
+      <c r="A10" s="16"/>
       <c r="B10" s="7" t="s">
         <v>11</v>
       </c>
@@ -843,19 +843,19 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
-      <c r="B11" s="13" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="11" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
+      <c r="A12" s="16"/>
       <c r="B12" s="7" t="s">
         <v>13</v>
       </c>
@@ -867,19 +867,19 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
-      <c r="B13" s="13" t="s">
+      <c r="A13" s="16"/>
+      <c r="B13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="11" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
+      <c r="A14" s="16"/>
       <c r="B14" s="7" t="s">
         <v>15</v>
       </c>
@@ -891,19 +891,19 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="11"/>
-      <c r="B15" s="15" t="s">
+      <c r="A15" s="17"/>
+      <c r="B15" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="13" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="18" t="s">
         <v>21</v>
       </c>
       <c r="B16" s="8" t="s">
@@ -917,19 +917,19 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="10"/>
-      <c r="B17" s="17" t="s">
+      <c r="A17" s="16"/>
+      <c r="B17" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="15" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
+      <c r="A18" s="16"/>
       <c r="B18" s="8" t="s">
         <v>3</v>
       </c>
@@ -941,19 +941,19 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
-      <c r="B19" s="17" t="s">
+      <c r="A19" s="16"/>
+      <c r="B19" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="15" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
+      <c r="A20" s="16"/>
       <c r="B20" s="8" t="s">
         <v>5</v>
       </c>
@@ -965,19 +965,19 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
-      <c r="B21" s="17" t="s">
+      <c r="A21" s="16"/>
+      <c r="B21" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="15" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
+      <c r="A22" s="16"/>
       <c r="B22" s="8" t="s">
         <v>7</v>
       </c>
@@ -989,19 +989,19 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="10"/>
-      <c r="B23" s="17" t="s">
+      <c r="A23" s="16"/>
+      <c r="B23" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="15" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
+      <c r="A24" s="16"/>
       <c r="B24" s="8" t="s">
         <v>8</v>
       </c>
@@ -1013,19 +1013,19 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="10"/>
-      <c r="B25" s="17" t="s">
+      <c r="A25" s="16"/>
+      <c r="B25" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="15" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="10"/>
+      <c r="A26" s="16"/>
       <c r="B26" s="8" t="s">
         <v>10</v>
       </c>
@@ -1037,19 +1037,19 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="10"/>
-      <c r="B27" s="17" t="s">
+      <c r="A27" s="16"/>
+      <c r="B27" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="15" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
+      <c r="A28" s="16"/>
       <c r="B28" s="8" t="s">
         <v>12</v>
       </c>
@@ -1061,19 +1061,19 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="10"/>
-      <c r="B29" s="17" t="s">
+      <c r="A29" s="16"/>
+      <c r="B29" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="15" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="10"/>
+      <c r="A30" s="16"/>
       <c r="B30" s="8" t="s">
         <v>14</v>
       </c>
@@ -1085,19 +1085,19 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="10"/>
-      <c r="B31" s="17" t="s">
+      <c r="A31" s="16"/>
+      <c r="B31" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="15" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="11"/>
+      <c r="A32" s="17"/>
       <c r="B32" s="9" t="s">
         <v>16</v>
       </c>
